--- a/backend/templates/BOM_1.xlsx
+++ b/backend/templates/BOM_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\docgen-platform\backend\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0A0EA7E-9272-4DEF-9ED0-F18F2DD333DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0D857C4-C049-4A56-AB07-3EED82ADCB12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-104" yWindow="-104" windowWidth="22326" windowHeight="11947" xr2:uid="{A5E7338C-5E6E-4A4C-9DF5-37B1037E6A05}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
   <si>
     <t>#</t>
   </si>
@@ -51,24 +51,9 @@
     <t>1.1</t>
   </si>
   <si>
-    <t>SUB-TOTAL  Equipements</t>
-  </si>
-  <si>
     <t>1.2</t>
   </si>
   <si>
-    <t>C8200L-1N-4T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Routeur SD-WAN multi-WAN </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Licence Cisco DNA Essentials </t>
-  </si>
-  <si>
-    <t>Licence (VPN IPsec, SD-WAN basique)</t>
-  </si>
-  <si>
     <t>Client : LPSA</t>
   </si>
   <si>
@@ -76,6 +61,18 @@
   </si>
   <si>
     <t>Unité</t>
+  </si>
+  <si>
+    <t>1.3</t>
+  </si>
+  <si>
+    <t>1.4</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>1.6</t>
   </si>
 </sst>
 </file>
@@ -85,7 +82,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-[$Ar]\ * #,##0.00_-;\-[$Ar]\ * #,##0.00_-;_-[$Ar]\ * &quot;-&quot;??_-;_-@_-" x16r2:formatCode16="_-[$Ar-mg-MG]\ * #,##0.00_-;\-[$Ar-mg-MG]\ * #,##0.00_-;_-[$Ar-mg-MG]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-[$Ar]\ * #,##0.00_-;\-[$Ar]\ * #,##0.00_-;_-[$Ar]\ * &quot;-&quot;??_-;_-@_-" x16r2:formatCode16="_-[$Ar-mg-MG]\ * #,##0.00_-;\-[$Ar-mg-MG]\ * #,##0.00_-;_-[$Ar-mg-MG]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -410,6 +407,21 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -419,15 +431,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -445,12 +448,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="16">
@@ -781,7 +778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BABFDAF0-E923-43C4-A174-28EA523A1C73}">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="16.09765625" customWidth="1"/>
@@ -793,18 +790,18 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="16" t="s">
+      <c r="C1" s="17"/>
+      <c r="D1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
       <c r="H1" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>4</v>
@@ -817,28 +814,28 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="19"/>
+      <c r="A2" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="21"/>
     </row>
     <row r="3" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="18"/>
+      <c r="B3" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="20"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -852,79 +849,125 @@
       <c r="A4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="9"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="14"/>
       <c r="H4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="6">
-        <v>1</v>
-      </c>
-      <c r="J4" s="20">
-        <v>6700000</v>
-      </c>
-      <c r="K4" s="20">
-        <v>6700000</v>
-      </c>
+      <c r="I4" s="6"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
     </row>
-    <row r="5" spans="1:11" ht="35.299999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="35.299999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="9"/>
+        <v>8</v>
+      </c>
+      <c r="B5" s="13"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="14"/>
       <c r="H5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="I5" s="6">
-        <v>1</v>
-      </c>
-      <c r="J5" s="20">
-        <v>500000</v>
-      </c>
-      <c r="K5" s="20">
-        <v>500000</v>
-      </c>
+      <c r="I5" s="6"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
     </row>
-    <row r="6" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="21">
+    <row r="6" spans="1:11" ht="35.299999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="13"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I6" s="6"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+    </row>
+    <row r="7" spans="1:11" ht="35.299999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="13"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I7" s="6"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+    </row>
+    <row r="8" spans="1:11" ht="35.299999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="13"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="6"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+    </row>
+    <row r="9" spans="1:11" ht="35.299999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="13"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="6"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+    </row>
+    <row r="10" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="10"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="9">
         <f>SUM(K4:K5)</f>
-        <v>7200000</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:11" ht="42.8" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="18" ht="30.85" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="20" ht="42.8" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" ht="30.85" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="17">
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="D5:G5"/>
     <mergeCell ref="B1:C1"/>
@@ -933,7 +976,15 @@
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="D4:G4"/>
-    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:G8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:G9"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
